--- a/Datos/zonasarbitraje.xlsx
+++ b/Datos/zonasarbitraje.xlsx
@@ -1,23 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruben\Desktop\autoref\Datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D116551F-7209-4A64-8C42-28F5A77AC8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ZonasArbitraje" r:id="rId1"/>
+    <sheet name="ZonasArbitraje" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Fecha de creación</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>19/10/2024 13:20</t>
+  </si>
+  <si>
+    <t>AvilesCorvera</t>
+  </si>
+  <si>
+    <t>19/10/2024 13:21</t>
+  </si>
+  <si>
+    <t>Cangas de Onis</t>
+  </si>
+  <si>
+    <t>19/10/2024 13:19</t>
+  </si>
+  <si>
+    <t>Gijón</t>
+  </si>
+  <si>
+    <t>Llanes</t>
+  </si>
+  <si>
+    <t>Nava</t>
+  </si>
+  <si>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>Siero</t>
+  </si>
+  <si>
+    <t>13/02/2025 22:25</t>
+  </si>
+  <si>
+    <t>Villaviciosa</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="yyyy/mm/dd" numFmtId="100"/>
-    <numFmt formatCode="yyyy/mm/dd hh:mm:ss" numFmtId="101"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
-      <sz val="11"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -29,36 +86,34 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="1">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -160,7 +215,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="false"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -189,7 +244,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -198,7 +253,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -207,7 +262,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -323,252 +378,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="5.5" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>Fecha de creación</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>Fecha de destrucción</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>search_text_cache</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:20</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>AvilesCorvera</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="n">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:21</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>Cangas de Onis</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:19</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>Gijón</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:20</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>Llanes</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="n">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>7</v>
       </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:21</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>Nava</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="n">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:20</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>Oviedo</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="n">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>19/10/2024 13:20</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>Siero</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="n">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>13/02/2025 22:25</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>Villaviciosa</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
-  <headerFooter/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>